--- a/src/pandorafits/formats/nirda/level0-ffi_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level0-ffi_nirda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chedges/Pandora/repos/pandora-fits/src/pandorafits/formats/nirda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB15E6FD-3130-964D-9570-DFE3711D02DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04307112-9362-4E4F-9FE9-D932951BBA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17220" activeTab="2" xr2:uid="{B6A127EC-86E5-1348-8EA3-CDC4E3346098}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="140">
   <si>
     <t>SIMPLE</t>
   </si>
@@ -266,9 +266,6 @@
   </si>
   <si>
     <t>CompImageHDU</t>
-  </si>
-  <si>
-    <t>Conforms to FITS standard</t>
   </si>
   <si>
     <t>File contains extensions</t>
@@ -1020,7 +1017,7 @@
         <v>20</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -1084,10 +1081,10 @@
         <v>34</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>52</v>
@@ -1098,10 +1095,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>53</v>
@@ -1126,7 +1123,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>55</v>
@@ -1159,10 +1156,10 @@
         <v>38</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -1310,266 +1307,266 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C31" s="6">
         <v>10</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C32" s="6">
         <v>53251</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C33" s="6">
         <v>0</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C34" s="6">
         <v>0</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C35" s="6">
         <v>37002</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C36" s="6">
         <v>1</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C37" s="6">
         <v>1</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C38" s="6">
         <v>0</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C39" s="6">
         <v>0</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C40" s="6">
         <v>0</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C41" s="6">
         <v>4</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1</v>
+      </c>
+      <c r="D42" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C43" s="6">
+        <v>1</v>
+      </c>
+      <c r="D43" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="C43" s="6">
-        <v>1</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0</v>
+      </c>
+      <c r="D44" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="C44" s="6">
-        <v>0</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C45" s="6">
         <v>0</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C46" s="6">
         <v>0</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C47" s="6">
         <v>5</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C48" s="6">
         <v>4</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C49" s="6">
         <v>4</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C50" s="6">
         <v>10736</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C51" s="6">
         <v>26.651636123657202</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C52" s="6">
         <v>298.25445556640602</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C53" s="6">
         <v>133.55955505371</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C54" s="6">
         <v>286.43704223632801</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
@@ -1681,7 +1678,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83271CB-FC54-E142-86E3-37282DC63805}">
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
@@ -1706,63 +1703,61 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>136</v>
-      </c>
     </row>
     <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="C3" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>76</v>
+      <c r="A3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6">
+        <v>16</v>
+      </c>
+      <c r="C3" s="6">
+        <v>16</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" s="6">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C4" s="6">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6">
-        <v>3</v>
-      </c>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="6"/>
       <c r="C5" s="6">
-        <v>3</v>
+        <v>2048</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
-        <v>21</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
+        <v>22</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6">
@@ -1774,11 +1769,11 @@
     </row>
     <row r="7" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6">
-        <v>2048</v>
+        <v>1</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>47</v>
@@ -1786,244 +1781,244 @@
     </row>
     <row r="8" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6">
         <v>1</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>47</v>
-      </c>
+      <c r="D8" s="6"/>
     </row>
     <row r="9" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="6"/>
+        <v>41</v>
+      </c>
+      <c r="B9" s="6">
+        <v>32768</v>
+      </c>
       <c r="C9" s="6">
-        <v>1</v>
+        <v>32768</v>
       </c>
       <c r="D9" s="6"/>
     </row>
     <row r="10" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="6">
-        <v>32768</v>
-      </c>
-      <c r="C10" s="6">
-        <v>32768</v>
-      </c>
-      <c r="D10" s="6"/>
+        <v>6</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>78</v>
+        <v>7</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="10">
+        <v>3</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13" s="6"/>
-      <c r="C13" s="10">
-        <v>3</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>48</v>
+      <c r="C13" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B15" s="6"/>
-      <c r="C15" s="6" t="b">
-        <v>1</v>
+      <c r="C15" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6" t="s">
         <v>79</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="B20" s="6"/>
-      <c r="C20" s="6" t="s">
-        <v>109</v>
+      <c r="C20" s="6">
+        <v>0</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6">
         <v>0</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B22" s="6"/>
-      <c r="C22" s="6">
-        <v>0</v>
+      <c r="C22" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B23" s="6"/>
-      <c r="C23" s="6" t="s">
-        <v>110</v>
+      <c r="C23" s="6">
+        <v>1</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6">
         <v>16</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6">
         <v>0</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2035,103 +2030,103 @@
         <v>0</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6">
-        <v>0</v>
+        <v>2048</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6">
         <v>2048</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6">
-        <v>2048</v>
+        <v>1</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6">
-        <v>11</v>
+        <v>1561</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6">
-        <v>1561</v>
+        <v>965000000</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
-        <v>17</v>
+        <v>110</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6">
-        <v>965000000</v>
+        <v>10</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2140,7 +2135,7 @@
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6">
-        <v>10</v>
+        <v>53251</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>82</v>
@@ -2152,7 +2147,7 @@
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6">
-        <v>53251</v>
+        <v>0</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>83</v>
@@ -2170,13 +2165,13 @@
         <v>84</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A40" s="9" t="s">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="6" t="s">
         <v>114</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6">
-        <v>0</v>
+        <v>37002</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>85</v>
@@ -2188,7 +2183,7 @@
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6">
-        <v>37002</v>
+        <v>1</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>86</v>
@@ -2212,7 +2207,7 @@
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>88</v>
@@ -2248,7 +2243,7 @@
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>91</v>
@@ -2256,11 +2251,11 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>92</v>
@@ -2268,43 +2263,43 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6">
         <v>1</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6">
         <v>1</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6">
@@ -2332,7 +2327,7 @@
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>101</v>
@@ -2344,10 +2339,10 @@
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
@@ -2368,34 +2363,34 @@
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6">
-        <v>4</v>
+        <v>10736</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="6">
-        <v>10736</v>
+        <v>26.651636123657202</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B58" s="6"/>
       <c r="C58" s="6">
-        <v>26.651636123657202</v>
+        <v>298.25445556640602</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -2404,7 +2399,7 @@
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="6">
-        <v>298.25445556640602</v>
+        <v>133.55955505371</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>130</v>
@@ -2416,7 +2411,7 @@
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="6">
-        <v>133.55955505371</v>
+        <v>286.43704223632801</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>131</v>
@@ -2424,54 +2419,42 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
-        <v>108</v>
+        <v>5</v>
       </c>
       <c r="B61" s="6"/>
-      <c r="C61" s="6">
-        <v>286.43704223632801</v>
+      <c r="C61" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>132</v>
+        <v>76</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>77</v>
+      <c r="A62" t="s">
+        <v>136</v>
+      </c>
+      <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
         <v>139</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
-      </c>
-      <c r="C64">
-        <v>1</v>
-      </c>
-      <c r="D64" t="s">
-        <v>140</v>
       </c>
     </row>
   </sheetData>
